--- a/documentation/Project Product Backlog.xlsx
+++ b/documentation/Project Product Backlog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28528"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lanthorr\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb00645\Desktop\Dev\DevOps_Project_Portfolio_Hub_Project\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DD06201-721F-40F7-B001-FEE609E159AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD3508B-4FE1-4E29-A52D-3025FAD68399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="0" windowWidth="19200" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -141,7 +141,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,7 +150,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -159,12 +159,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -172,16 +178,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,14 +516,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.5703125" customWidth="1"/>
-    <col min="4" max="4" width="77.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.54296875" customWidth="1"/>
+    <col min="4" max="4" width="77.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,203 +533,203 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="9">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="9">
         <v>1</v>
       </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="10">
         <v>2</v>
       </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="9">
         <v>2</v>
       </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="10">
         <v>2</v>
       </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="9">
         <v>2</v>
       </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="10">
         <v>3</v>
       </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="B11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="9">
         <v>3</v>
       </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="10">
         <v>3</v>
       </c>
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="B13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A14">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="2" t="s">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="9">
+        <v>4</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="2" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="10">
+        <v>4</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="8" t="s">
         <v>32</v>
       </c>
     </row>

--- a/documentation/Project Product Backlog.xlsx
+++ b/documentation/Project Product Backlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb00645\Desktop\Dev\DevOps_Project_Portfolio_Hub_Project\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD3508B-4FE1-4E29-A52D-3025FAD68399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA1A2B8-F714-4971-BBBC-A3448880E300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="0" windowWidth="19200" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12540" yWindow="11670" windowWidth="14640" windowHeight="9270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/documentation/Project Product Backlog.xlsx
+++ b/documentation/Project Product Backlog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb00645\Desktop\Dev\DevOps_Project_Portfolio_Hub_Project\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb00645\Desktop\Project 2\DevOps_Project_Portfolio_Hub_Project\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA1A2B8-F714-4971-BBBC-A3448880E300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111C226C-D253-4C2D-A317-FEBFA6987962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12540" yWindow="11670" windowWidth="14640" windowHeight="9270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>Priority</t>
   </si>
@@ -50,91 +50,109 @@
     <t>So that…</t>
   </si>
   <si>
-    <t>User</t>
-  </si>
-  <si>
     <t>Upload project files</t>
   </si>
   <si>
     <t>I can store and organize my work</t>
   </si>
   <si>
-    <t>Categorize projects</t>
-  </si>
-  <si>
-    <t>I can find relevant work easily</t>
-  </si>
-  <si>
-    <t>View individual project pages</t>
-  </si>
-  <si>
-    <t>I can showcase my work professionally</t>
-  </si>
-  <si>
     <t>Customize my portfolio</t>
   </si>
   <si>
-    <t>I can highlight my skills and projects effectively</t>
-  </si>
-  <si>
-    <t>Filter projects by category and tags</t>
-  </si>
-  <si>
-    <t>I can quickly find specific types of projects</t>
-  </si>
-  <si>
-    <t>Link hosted projects</t>
-  </si>
-  <si>
-    <t>I can provide live demos of my work</t>
-  </si>
-  <si>
     <t>Edit and delete projects</t>
   </si>
   <si>
-    <t>I can keep my portfolio up to date</t>
-  </si>
-  <si>
     <t>Add repository links and resources</t>
   </si>
   <si>
-    <t>I can share additional project details</t>
-  </si>
-  <si>
     <t>Set project visibility (public/private)</t>
   </si>
   <si>
     <t>I can control who sees my work</t>
   </si>
   <si>
-    <t>Create and manage an account</t>
-  </si>
-  <si>
-    <t>I can save and manage my projects</t>
-  </si>
-  <si>
-    <t>Secure my account with authentication</t>
-  </si>
-  <si>
-    <t>I can protect my data</t>
-  </si>
-  <si>
     <t>Preview my portfolio</t>
   </si>
   <si>
-    <t>I can see how it looks to others</t>
-  </si>
-  <si>
-    <t>Ensure responsive design for project pages</t>
-  </si>
-  <si>
-    <t>I can have a seamless experience across devices</t>
-  </si>
-  <si>
-    <t>Use a dashboard to manage all projects</t>
-  </si>
-  <si>
-    <t>I can efficiently organize my work</t>
+    <t>Anonymous user</t>
+  </si>
+  <si>
+    <t>I can explore the platform before creating an account</t>
+  </si>
+  <si>
+    <t>View individual public project pages</t>
+  </si>
+  <si>
+    <t>I can browse other users’ work without logging in</t>
+  </si>
+  <si>
+    <t>Sign in to my account</t>
+  </si>
+  <si>
+    <t>I can access my personal projects and settings</t>
+  </si>
+  <si>
+    <t>Create an account</t>
+  </si>
+  <si>
+    <t>I can start uploading and managing my own portfolio</t>
+  </si>
+  <si>
+    <t>Signed-in user</t>
+  </si>
+  <si>
+    <t>I can highlight my skills and work effectively</t>
+  </si>
+  <si>
+    <t>Link hosted project URLs</t>
+  </si>
+  <si>
+    <t>I can provide live demos or external links</t>
+  </si>
+  <si>
+    <t>I can share more technical details about my work</t>
+  </si>
+  <si>
+    <t>I can keep my portfolio accurate and up to date</t>
+  </si>
+  <si>
+    <t>Update account information</t>
+  </si>
+  <si>
+    <t>I can keep my profile details current</t>
+  </si>
+  <si>
+    <t>Delete my account</t>
+  </si>
+  <si>
+    <t>I can remove my presence from the platform if needed</t>
+  </si>
+  <si>
+    <t>Log out</t>
+  </si>
+  <si>
+    <t>I can end my session securely</t>
+  </si>
+  <si>
+    <t>I can view how my profile appears to others</t>
+  </si>
+  <si>
+    <t>Any user</t>
+  </si>
+  <si>
+    <t>View a responsive layout across all devices</t>
+  </si>
+  <si>
+    <t>I can browse projects comfortably on mobile or desktop</t>
+  </si>
+  <si>
+    <t>Use a dashboard to manage all my projects</t>
+  </si>
+  <si>
+    <t>I can efficiently organize and access my work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access the home page </t>
   </si>
 </sst>
 </file>
@@ -165,7 +183,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -219,22 +237,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -515,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
@@ -533,210 +557,239 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="6">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="7" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="10">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="6">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>2</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="6">
+        <v>2</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>2</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="6">
+        <v>2</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>3</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="6">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>3</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="6">
         <v>4</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="9">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="B16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="10">
-        <v>1</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="9">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="10">
-        <v>2</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="9">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="10">
-        <v>2</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="9">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="10">
-        <v>3</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="9">
-        <v>3</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="10">
-        <v>3</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9">
-        <v>4</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="10">
-        <v>4</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>32</v>
+      <c r="B17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D20">
-    <sortCondition ref="A2:A20"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:D3">
+    <sortCondition ref="A1:A3"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>